--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97439</v>
+        <v>97442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97442</v>
+        <v>97443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97443</v>
+        <v>97448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97448</v>
+        <v>97450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
